--- a/etf_holdings/2026-09-15_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:58</t>
+          <t>2026-09-15 21:12:21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1.24%2380</t>
+          <t>+0.21%2385</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2380</v>
+        <v>2385</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15.36%9,800,000</t>
+          <t>15.71%9,800,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>15.36%</t>
+          <t>15.71%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:58</t>
+          <t>2026-09-15 21:12:21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.55%4560</t>
+          <t>-2.85%4430</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4560</v>
+        <v>4430</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.64%2,210,000</t>
+          <t>6.58%2,210,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.64%</t>
+          <t>6.58%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:58</t>
+          <t>2026-09-15 21:12:21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-1.78%3310</t>
+          <t>-5.89%3115</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-1.78%</t>
+          <t>-5.89%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3310</v>
+        <v>3115</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.21%2,850,000</t>
+          <t>5.97%2,850,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.21%</t>
+          <t>5.97%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.37%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:58</t>
+          <t>2026-09-15 21:12:21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.37%5345</t>
+          <t>-4.3%5115</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5345</v>
+        <v>5115</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.63%1,600,000</t>
+          <t>5.50%1,600,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.63%</t>
+          <t>5.50%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:58</t>
+          <t>2026-09-15 21:12:21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.72%970</t>
+          <t>-1.96%951</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.72%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>970</v>
+        <v>951</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.40%8,460,000</t>
+          <t>5.41%8,460,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.40%</t>
+          <t>5.41%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:58</t>
+          <t>2026-09-15 21:12:21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+1.42%142.5</t>
+          <t>-2.81%138.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+1.42%</t>
+          <t>-2.81%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>142.5</v>
+        <v>138.5</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.16%55,000,000</t>
+          <t>5.12%55,000,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.16%</t>
+          <t>5.12%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:58</t>
+          <t>2026-09-15 21:12:21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+0.95%5820</t>
+          <t>-2.77%5440</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+0.95%</t>
+          <t>-2.77%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5820</v>
+        <v>5440</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.27%1,115,000</t>
+          <t>4.02%1,100,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.27%</t>
+          <t>4.02%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1115000</v>
+        <v>1100000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:58</t>
+          <t>2026-09-15 21:12:21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0%5620</t>
+          <t>-8.76%5310</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-8.76%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5620</v>
+        <v>5310</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.05%1,100,000</t>
+          <t>3.98%1,115,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.05%</t>
+          <t>3.98%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1100000</v>
+        <v>1115000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:58</t>
+          <t>2026-09-15 21:12:21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-1.73%2270</t>
+          <t>+3.09%1670</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+3.09%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2270</v>
+        <v>1670</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.97%1,987,956</t>
+          <t>3.09%2,750,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>3.09%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1987956</v>
+        <v>2750000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:58</t>
+          <t>2026-09-15 21:12:21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0%1620</t>
+          <t>+1.98%2315</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+1.98%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1620</v>
+        <v>2315</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.93%2,750,000</t>
+          <t>3.09%1,987,956</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>3.09%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>2750000</v>
+        <v>1987956</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:58</t>
+          <t>2026-09-15 21:12:21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+0.18%545</t>
+          <t>-1.47%537</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.87%8,000,000</t>
+          <t>2.89%8,000,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.87%</t>
+          <t>2.89%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:58</t>
+          <t>2026-09-15 21:12:21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-0.53%1875</t>
+          <t>-1.87%1840</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1875</v>
+        <v>1840</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:58</t>
+          <t>2026-09-15 21:12:21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+4.58%6400</t>
+          <t>-5.7%6035</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+4.58%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>6400</v>
+        <v>6035</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.61%620,000</t>
+          <t>2.51%620,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>2.51%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:58</t>
+          <t>2026-09-15 21:12:21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-9.98%5995</t>
+          <t>+2.84%1085</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-9.98%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5995</v>
+        <v>1085</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.12%536,000</t>
+          <t>2.02%2,770,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>2.02%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>536000</v>
+        <v>2770000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:58</t>
+          <t>2026-09-15 21:12:21</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.21%234</t>
+          <t>-5.34%221.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-5.34%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>234</v>
+        <v>221.5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.08%13,500,000</t>
+          <t>2.01%13,500,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>2.01%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:59</t>
+          <t>2026-09-15 21:12:22</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,33 +1424,33 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-2.92%798</t>
+          <t>-0.38%795</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-2.92%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.87%3,550,000</t>
+          <t>1.98%3,700,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>3550000</v>
+        <v>3700000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:59</t>
+          <t>2026-09-15 21:12:22</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-2.31%1055</t>
+          <t>-2.84%1370</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-2.31%</t>
+          <t>-2.84%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1055</v>
+        <v>1370</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.83%2,640,000</t>
+          <t>1.75%1,900,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>2640000</v>
+        <v>1900000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:59</t>
+          <t>2026-09-15 21:12:22</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-2.15%1365</t>
+          <t>+1.28%1980</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-2.15%</t>
+          <t>+1.28%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1365</v>
+        <v>1980</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.76%1,900,000</t>
+          <t>1.72%1,293,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.76%</t>
+          <t>1.72%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>1900000</v>
+        <v>1293000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:59</t>
+          <t>2026-09-15 21:12:22</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>6488環球晶</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+4.27%1955</t>
+          <t>+1.56%914</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+4.27%</t>
+          <t>+1.56%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1955</v>
+        <v>914</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.66%1,293,000</t>
+          <t>1.72%2,800,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.72%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>1293000</v>
+        <v>2800000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:59</t>
+          <t>2026-09-15 21:12:22</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>6488環球晶</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-1.64%902</t>
+          <t>+1%6055</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-1.64%</t>
+          <t>+1%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>902</v>
+        <v>6055</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.66%2,800,000</t>
+          <t>1.55%380,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.55%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>2800000</v>
+        <v>380000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:59</t>
+          <t>2026-09-15 21:12:22</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,25 +1729,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-4.36%17885</t>
+          <t>-2.56%17520</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-4.36%</t>
+          <t>-2.56%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>17885</v>
+        <v>17520</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.43%120,500</t>
+          <t>1.42%120,500</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:59</t>
+          <t>2026-09-15 21:12:22</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,25 +1790,25 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-0.93%2140</t>
+          <t>-2.8%2080</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2140</v>
+        <v>2080</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.41%1,000,000</t>
+          <t>1.40%1,000,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.40%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:59</t>
+          <t>2026-09-15 21:12:22</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,25 +1851,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-7.14%1235</t>
+          <t>-1.21%1220</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-7.14%</t>
+          <t>-1.21%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1235</v>
+        <v>1220</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.29%1,580,000</t>
+          <t>1.30%1,580,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:59</t>
+          <t>2026-09-15 21:12:22</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,25 +1912,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+0.7%2165</t>
+          <t>-6.47%2025</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+0.7%</t>
+          <t>-6.47%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2165</v>
+        <v>2025</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.08%760,000</t>
+          <t>1.03%760,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.03%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:59</t>
+          <t>2026-09-15 21:12:22</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,25 +1973,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-0.55%271.5</t>
+          <t>-1.29%268</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>271.5</v>
+        <v>268</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.96%5,360,000</t>
+          <t>0.97%5,360,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.97%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:59</t>
+          <t>2026-09-15 21:12:22</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,34 +2029,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>7769鴻勁</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-0.97%612</t>
+          <t>-2.7%6135</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>612</v>
+        <v>6135</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.81%2,000,000</t>
+          <t>0.54%130,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>2000000</v>
+        <v>130000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:59</t>
+          <t>2026-09-15 21:12:22</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,34 +2090,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>7769鴻勁</t>
+          <t>2317鴻海</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-0.08%6305</t>
+          <t>-0.8%246.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>6305</v>
+        <v>246.5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.54%130,000</t>
+          <t>0.53%3,200,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.53%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>130000</v>
+        <v>3200000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:59</t>
+          <t>2026-09-15 21:12:22</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2317鴻海</t>
+          <t>3211順達</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+0.2%248.5</t>
+          <t>-0.41%361</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+0.2%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>248.5</v>
+        <v>361</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.52%3,200,000</t>
+          <t>0.49%2,000,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>3200000</v>
+        <v>2000000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:59</t>
+          <t>2026-09-15 21:12:22</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3211順達</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-3.21%362</t>
+          <t>-1.72%257</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-3.21%</t>
+          <t>-1.72%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>362</v>
+        <v>257</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.48%2,000,000</t>
+          <t>0.45%2,600,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>2000000</v>
+        <v>2600000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:59</t>
+          <t>2026-09-15 21:12:22</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-0.57%261.5</t>
+          <t>-3.27%592</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-0.57%</t>
+          <t>-3.27%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>261.5</v>
+        <v>592</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.45%2,600,000</t>
+          <t>0.40%1,000,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>2600000</v>
+        <v>1000000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:01</t>
+          <t>2026-09-15 21:12:23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,25 +2339,25 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-4.79%1590</t>
+          <t>-5.03%1510</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-4.79%</t>
+          <t>-5.03%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1590</v>
+        <v>1510</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.37%350,000</t>
+          <t>0.36%350,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:01</t>
+          <t>2026-09-15 21:12:23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,25 +2400,25 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-0.59%509</t>
+          <t>-3.24%492.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>-3.24%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>509</v>
+        <v>492.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.37%1,100,000</t>
+          <t>0.36%1,100,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:01</t>
+          <t>2026-09-15 21:12:23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,16 +2461,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-2.98%683</t>
+          <t>-2.78%664</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-2.98%</t>
+          <t>-2.78%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>683</v>
+        <v>664</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:01</t>
+          <t>2026-09-15 21:12:23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+6%159</t>
+          <t>-3.46%153.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+6%</t>
+          <t>-3.46%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>159</v>
+        <v>153.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:01</t>
+          <t>2026-09-15 21:12:23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+1.81%112.5</t>
+          <t>-2.22%110</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+1.81%</t>
+          <t>-2.22%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>112.5</v>
+        <v>110</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:01</t>
+          <t>2026-09-15 21:12:23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-0.75%11990</t>
+          <t>-2.29%11715</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>-2.29%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>11990</v>
+        <v>11715</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:01</t>
+          <t>2026-09-15 21:12:23</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,25 +2705,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+0.63%1590</t>
+          <t>-4.4%1520</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+0.63%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1590</v>
+        <v>1520</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.21%200,000</t>
+          <t>0.20%200,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:01</t>
+          <t>2026-09-15 21:12:23</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+1%1015</t>
+          <t>+1.97%1035</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+1%</t>
+          <t>+1.97%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1015</v>
+        <v>1035</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:01</t>
+          <t>2026-09-15 21:12:23</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,25 +2827,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+3.88%535</t>
+          <t>-2.8%520</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+3.88%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>535</v>
+        <v>520</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.14%386,000</t>
+          <t>0.13%386,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:01</t>
+          <t>2026-09-15 21:12:23</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-3.96%230.5</t>
+          <t>-2.86%221</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-3.96%</t>
+          <t>-2.86%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>230.5</v>
+        <v>221</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:01</t>
+          <t>2026-09-15 21:12:23</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-4.68%753</t>
+          <t>-2.39%735</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-4.68%</t>
+          <t>-2.39%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>753</v>
+        <v>735</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:01</t>
+          <t>2026-09-15 21:12:23</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-2.4%69.2</t>
+          <t>-1.59%68.1</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-1.59%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>69.2</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:01</t>
+          <t>2026-09-15 21:12:23</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,34 +3066,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>6285啟碁</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-0.22%222</t>
+          <t>-1.26%274</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>-1.26%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>222</v>
+        <v>274</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.05%350,000</t>
+          <t>0.06%300,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.06%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>350000</v>
+        <v>300000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:01</t>
+          <t>2026-09-15 21:12:23</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,25 +3127,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>6285啟碁</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+0.18%277.5</t>
+          <t>0%222</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>277.5</v>
+        <v>222</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.05%300,000</t>
+          <t>0.05%350,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>300000</v>
+        <v>350000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:01</t>
+          <t>2026-09-15 21:12:23</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-6.91%485</t>
+          <t>-6.95%482</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-6.91%</t>
+          <t>-6.95%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:02</t>
+          <t>2026-09-15 21:12:25</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,16 +3254,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-2.52%116</t>
+          <t>-1.29%114.5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-2.52%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>116</v>
+        <v>114.5</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:02</t>
+          <t>2026-09-15 21:12:25</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-3.63%1990</t>
+          <t>-0.78%1920</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-3.63%</t>
+          <t>-0.78%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1990</v>
+        <v>1920</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:02</t>
+          <t>2026-09-15 21:12:25</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+1.76%520</t>
+          <t>-0.38%518</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+1.76%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:02</t>
+          <t>2026-09-15 21:12:25</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-9.89%323.5</t>
+          <t>+1.7%329</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-9.89%</t>
+          <t>+1.7%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>323.5</v>
+        <v>329</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:02</t>
+          <t>2026-09-15 21:12:25</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-6.71%160</t>
+          <t>-0.31%159.5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-6.71%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>160</v>
+        <v>159.5</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-09-15_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:21</t>
+          <t>2026-09-15 22:22:37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:21</t>
+          <t>2026-09-15 22:22:37</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:21</t>
+          <t>2026-09-15 22:22:37</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:21</t>
+          <t>2026-09-15 22:22:37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:21</t>
+          <t>2026-09-15 22:22:37</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:21</t>
+          <t>2026-09-15 22:22:37</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:21</t>
+          <t>2026-09-15 22:22:37</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:21</t>
+          <t>2026-09-15 22:22:37</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:21</t>
+          <t>2026-09-15 22:22:37</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:21</t>
+          <t>2026-09-15 22:22:37</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:21</t>
+          <t>2026-09-15 22:22:37</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:21</t>
+          <t>2026-09-15 22:22:37</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:21</t>
+          <t>2026-09-15 22:22:37</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:21</t>
+          <t>2026-09-15 22:22:37</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:21</t>
+          <t>2026-09-15 22:22:37</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:22</t>
+          <t>2026-09-15 22:22:39</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:22</t>
+          <t>2026-09-15 22:22:39</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:22</t>
+          <t>2026-09-15 22:22:39</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:22</t>
+          <t>2026-09-15 22:22:39</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:22</t>
+          <t>2026-09-15 22:22:39</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:22</t>
+          <t>2026-09-15 22:22:39</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:22</t>
+          <t>2026-09-15 22:22:39</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:22</t>
+          <t>2026-09-15 22:22:39</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:22</t>
+          <t>2026-09-15 22:22:39</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:22</t>
+          <t>2026-09-15 22:22:39</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:22</t>
+          <t>2026-09-15 22:22:39</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:22</t>
+          <t>2026-09-15 22:22:39</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:22</t>
+          <t>2026-09-15 22:22:39</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:22</t>
+          <t>2026-09-15 22:22:39</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:22</t>
+          <t>2026-09-15 22:22:39</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:23</t>
+          <t>2026-09-15 22:22:40</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:23</t>
+          <t>2026-09-15 22:22:40</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:23</t>
+          <t>2026-09-15 22:22:40</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:23</t>
+          <t>2026-09-15 22:22:40</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:23</t>
+          <t>2026-09-15 22:22:40</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:23</t>
+          <t>2026-09-15 22:22:40</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:23</t>
+          <t>2026-09-15 22:22:40</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:23</t>
+          <t>2026-09-15 22:22:40</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:23</t>
+          <t>2026-09-15 22:22:40</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:23</t>
+          <t>2026-09-15 22:22:40</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:23</t>
+          <t>2026-09-15 22:22:40</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:23</t>
+          <t>2026-09-15 22:22:40</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:23</t>
+          <t>2026-09-15 22:22:40</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:23</t>
+          <t>2026-09-15 22:22:40</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:23</t>
+          <t>2026-09-15 22:22:40</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:25</t>
+          <t>2026-09-15 22:22:41</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:25</t>
+          <t>2026-09-15 22:22:41</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:25</t>
+          <t>2026-09-15 22:22:41</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:25</t>
+          <t>2026-09-15 22:22:41</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:25</t>
+          <t>2026-09-15 22:22:41</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-15_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:37</t>
+          <t>2026-09-15 22:28:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:37</t>
+          <t>2026-09-15 22:28:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:37</t>
+          <t>2026-09-15 22:28:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:37</t>
+          <t>2026-09-15 22:28:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:37</t>
+          <t>2026-09-15 22:28:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:37</t>
+          <t>2026-09-15 22:28:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:37</t>
+          <t>2026-09-15 22:28:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:37</t>
+          <t>2026-09-15 22:28:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:37</t>
+          <t>2026-09-15 22:28:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:37</t>
+          <t>2026-09-15 22:28:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:37</t>
+          <t>2026-09-15 22:28:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:37</t>
+          <t>2026-09-15 22:28:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:37</t>
+          <t>2026-09-15 22:28:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:37</t>
+          <t>2026-09-15 22:28:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:37</t>
+          <t>2026-09-15 22:28:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:39</t>
+          <t>2026-09-15 22:28:31</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:39</t>
+          <t>2026-09-15 22:28:31</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:39</t>
+          <t>2026-09-15 22:28:31</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:39</t>
+          <t>2026-09-15 22:28:31</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:39</t>
+          <t>2026-09-15 22:28:31</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:39</t>
+          <t>2026-09-15 22:28:31</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:39</t>
+          <t>2026-09-15 22:28:31</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:39</t>
+          <t>2026-09-15 22:28:31</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:39</t>
+          <t>2026-09-15 22:28:31</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:39</t>
+          <t>2026-09-15 22:28:31</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:39</t>
+          <t>2026-09-15 22:28:31</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:39</t>
+          <t>2026-09-15 22:28:31</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:39</t>
+          <t>2026-09-15 22:28:31</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:39</t>
+          <t>2026-09-15 22:28:31</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:39</t>
+          <t>2026-09-15 22:28:31</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:40</t>
+          <t>2026-09-15 22:28:33</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:40</t>
+          <t>2026-09-15 22:28:33</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:40</t>
+          <t>2026-09-15 22:28:33</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:40</t>
+          <t>2026-09-15 22:28:33</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:40</t>
+          <t>2026-09-15 22:28:33</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:40</t>
+          <t>2026-09-15 22:28:33</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:40</t>
+          <t>2026-09-15 22:28:33</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:40</t>
+          <t>2026-09-15 22:28:33</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:40</t>
+          <t>2026-09-15 22:28:33</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:40</t>
+          <t>2026-09-15 22:28:33</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:40</t>
+          <t>2026-09-15 22:28:33</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:40</t>
+          <t>2026-09-15 22:28:33</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:40</t>
+          <t>2026-09-15 22:28:33</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:40</t>
+          <t>2026-09-15 22:28:33</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:40</t>
+          <t>2026-09-15 22:28:33</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:41</t>
+          <t>2026-09-15 22:28:34</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:41</t>
+          <t>2026-09-15 22:28:34</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:41</t>
+          <t>2026-09-15 22:28:34</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:41</t>
+          <t>2026-09-15 22:28:34</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:41</t>
+          <t>2026-09-15 22:28:34</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
